--- a/data/1_raw/Ultimas.xlsx
+++ b/data/1_raw/Ultimas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bolsadesantiago.sharepoint.com/sites/Informacin-Derivex/Documentos compartidos/Información Derivex/3. Administración del Mercado/2. Administrar la Operación/Negociación de contratos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniminuto0-my.sharepoint.com/personal/jhon_tascon_uniminuto_edu/Documents/Documentos/GitHub/bot_futuros/data/1_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{AB835458-3EDA-40DD-89C5-D4BE41759EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{727229F6-FFFC-405F-95E3-CB2B5DA5434A}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{AB835458-3EDA-40DD-89C5-D4BE41759EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{814B5E17-E535-42C8-82BB-4380DFC87A31}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CB94E36F-ED36-4828-B896-BAF384ACAF5A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{CB94E36F-ED36-4828-B896-BAF384ACAF5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Negociaciones" sheetId="1" r:id="rId1"/>
@@ -1359,7 +1359,7 @@
     <col min="2" max="2" width="12" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="12" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" style="3" customWidth="1"/>
@@ -11195,6 +11195,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100BFCDF2566B3FF342A26CA12F0529358D" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="3f4c42a16b78b152d1720b28536737d0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="df062920-4020-40dc-9015-c52fc1b6f476" xmlns:ns3="72e9f21c-8664-4aad-aa68-4f5e72fc5d76" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ef8d5f0279a041615cce69704fa4e54" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11452,7 +11461,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="df062920-4020-40dc-9015-c52fc1b6f476">
@@ -11465,16 +11474,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7244A3-5556-4455-8231-85DEE5EC0FA3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B9E0C56-1762-4151-8930-626235C683FA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11494,7 +11502,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3780D0D0-C712-4B3E-8FD9-C471C8D147BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -11510,12 +11518,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7244A3-5556-4455-8231-85DEE5EC0FA3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>